--- a/ReSourceTracker/data-raw/PermittedPOTW.xlsx
+++ b/ReSourceTracker/data-raw/PermittedPOTW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu.sharepoint.com/sites/CEAE-Masters_Research_Group/Shared Documents/General/Boenisch-Oakes, Kylie/Research/Chapter 4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kylieboenischoakes/Documents/ResourceTracker/ReSourceTracker/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{22181680-7729-934A-AACE-AFCE583CE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0A3D2C5-F3ED-3042-9B1C-335DF02B108C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4D0416-91AB-254C-85B2-BC4BE8B498E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{1EFE79D8-E86D-494B-8A17-9BCECD28B3B3}"/>
+    <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{1EFE79D8-E86D-494B-8A17-9BCECD28B3B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Colordo WWTP Outfalls" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4979" uniqueCount="1076">
   <si>
     <t>EXTERNAL_PERMIT_NMBR</t>
   </si>
@@ -3264,13 +3264,16 @@
   </si>
   <si>
     <t>BOULDER CREEK</t>
+  </si>
+  <si>
+    <t></t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3284,6 +3287,11 @@
       <color rgb="FF0B57D0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Google Symbols"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3306,10 +3314,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3325,10 +3334,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3648,13 +3653,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B7DC3E-A36C-1846-B0DD-7107AEF1D1CD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AM251"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="17" max="17" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3773,7 +3779,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" hidden="1">
       <c r="A2" t="s">
         <v>423</v>
       </c>
@@ -3868,7 +3874,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" hidden="1">
       <c r="A3" t="s">
         <v>423</v>
       </c>
@@ -3963,7 +3969,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" hidden="1">
       <c r="A4" t="s">
         <v>431</v>
       </c>
@@ -4058,7 +4064,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" hidden="1">
       <c r="A5" t="s">
         <v>437</v>
       </c>
@@ -4156,7 +4162,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" hidden="1">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -4254,7 +4260,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" hidden="1">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -4352,7 +4358,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" hidden="1">
       <c r="A8" t="s">
         <v>447</v>
       </c>
@@ -4450,7 +4456,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" hidden="1">
       <c r="A9" t="s">
         <v>454</v>
       </c>
@@ -4551,7 +4557,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" hidden="1">
       <c r="A10" t="s">
         <v>460</v>
       </c>
@@ -4649,7 +4655,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" hidden="1">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -4750,7 +4756,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" hidden="1">
       <c r="A12" t="s">
         <v>466</v>
       </c>
@@ -4848,7 +4854,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" hidden="1">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -4943,7 +4949,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" hidden="1">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -5038,7 +5044,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" hidden="1">
       <c r="A15" t="s">
         <v>475</v>
       </c>
@@ -5133,7 +5139,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" hidden="1">
       <c r="A16" t="s">
         <v>481</v>
       </c>
@@ -5231,7 +5237,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:39" hidden="1">
       <c r="A17" t="s">
         <v>487</v>
       </c>
@@ -5329,7 +5335,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:39" hidden="1">
       <c r="A18" t="s">
         <v>492</v>
       </c>
@@ -5424,7 +5430,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:39" hidden="1">
       <c r="A19" t="s">
         <v>496</v>
       </c>
@@ -5522,7 +5528,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:39" hidden="1">
       <c r="A20" t="s">
         <v>500</v>
       </c>
@@ -5620,7 +5626,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:39" hidden="1">
       <c r="A21" t="s">
         <v>507</v>
       </c>
@@ -5718,7 +5724,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:39" hidden="1">
       <c r="A22" t="s">
         <v>512</v>
       </c>
@@ -5816,7 +5822,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:39" hidden="1">
       <c r="A23" t="s">
         <v>517</v>
       </c>
@@ -5911,7 +5917,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:39" hidden="1">
       <c r="A24" t="s">
         <v>524</v>
       </c>
@@ -6006,7 +6012,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:39" hidden="1">
       <c r="A25" t="s">
         <v>524</v>
       </c>
@@ -6101,7 +6107,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:39" hidden="1">
       <c r="A26" t="s">
         <v>524</v>
       </c>
@@ -6196,7 +6202,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:39" hidden="1">
       <c r="A27" t="s">
         <v>532</v>
       </c>
@@ -6291,7 +6297,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:39" hidden="1">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -6386,7 +6392,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:39" hidden="1">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -6481,7 +6487,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:39" hidden="1">
       <c r="A30" t="s">
         <v>98</v>
       </c>
@@ -6576,7 +6582,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:39" hidden="1">
       <c r="A31" t="s">
         <v>539</v>
       </c>
@@ -6674,7 +6680,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:39" hidden="1">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -6772,7 +6778,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" hidden="1">
       <c r="A33" t="s">
         <v>109</v>
       </c>
@@ -6870,7 +6876,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" hidden="1">
       <c r="A34" t="s">
         <v>546</v>
       </c>
@@ -6968,7 +6974,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:39" hidden="1">
       <c r="A35" t="s">
         <v>552</v>
       </c>
@@ -7066,7 +7072,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:39" hidden="1">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -7164,7 +7170,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:39" hidden="1">
       <c r="A37" t="s">
         <v>124</v>
       </c>
@@ -7259,7 +7265,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:39" hidden="1">
       <c r="A38" t="s">
         <v>557</v>
       </c>
@@ -7354,7 +7360,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:39" hidden="1">
       <c r="A39" t="s">
         <v>557</v>
       </c>
@@ -7449,7 +7455,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:39" hidden="1">
       <c r="A40" t="s">
         <v>557</v>
       </c>
@@ -7544,7 +7550,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:39" hidden="1">
       <c r="A41" t="s">
         <v>564</v>
       </c>
@@ -7642,7 +7648,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:39" hidden="1">
       <c r="A42" t="s">
         <v>130</v>
       </c>
@@ -7740,7 +7746,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:39" hidden="1">
       <c r="A43" t="s">
         <v>571</v>
       </c>
@@ -7838,7 +7844,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:39" hidden="1">
       <c r="A44" t="s">
         <v>576</v>
       </c>
@@ -7933,7 +7939,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:39" hidden="1">
       <c r="A45" t="s">
         <v>580</v>
       </c>
@@ -8031,7 +8037,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:39" hidden="1">
       <c r="A46" t="s">
         <v>137</v>
       </c>
@@ -8126,7 +8132,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:39" hidden="1">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -8227,7 +8233,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:39" hidden="1">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -8322,7 +8328,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:39" hidden="1">
       <c r="A49" t="s">
         <v>157</v>
       </c>
@@ -8417,7 +8423,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:39" hidden="1">
       <c r="A50" t="s">
         <v>587</v>
       </c>
@@ -8512,7 +8518,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:39" hidden="1">
       <c r="A51" t="s">
         <v>591</v>
       </c>
@@ -8607,7 +8613,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:39" hidden="1">
       <c r="A52" t="s">
         <v>596</v>
       </c>
@@ -8705,7 +8711,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:39" hidden="1">
       <c r="A53" t="s">
         <v>601</v>
       </c>
@@ -8800,7 +8806,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:39" hidden="1">
       <c r="A54" t="s">
         <v>607</v>
       </c>
@@ -8898,7 +8904,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:39" hidden="1">
       <c r="A55" t="s">
         <v>613</v>
       </c>
@@ -8993,7 +8999,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:39" hidden="1">
       <c r="A56" t="s">
         <v>613</v>
       </c>
@@ -9088,7 +9094,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:39" hidden="1">
       <c r="A57" t="s">
         <v>620</v>
       </c>
@@ -9189,7 +9195,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:39" hidden="1">
       <c r="A58" t="s">
         <v>620</v>
       </c>
@@ -9290,7 +9296,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="59" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:39" hidden="1">
       <c r="A59" t="s">
         <v>620</v>
       </c>
@@ -9391,7 +9397,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="60" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:39" hidden="1">
       <c r="A60" t="s">
         <v>628</v>
       </c>
@@ -9486,7 +9492,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="61" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:39" hidden="1">
       <c r="A61" t="s">
         <v>162</v>
       </c>
@@ -9587,7 +9593,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="62" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:39" hidden="1">
       <c r="A62" t="s">
         <v>168</v>
       </c>
@@ -9685,7 +9691,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="63" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:39" hidden="1">
       <c r="A63" t="s">
         <v>633</v>
       </c>
@@ -9783,7 +9789,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="64" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:39" hidden="1">
       <c r="A64" t="s">
         <v>173</v>
       </c>
@@ -9881,7 +9887,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="65" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:39" hidden="1">
       <c r="A65" t="s">
         <v>640</v>
       </c>
@@ -9979,7 +9985,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="66" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:39" hidden="1">
       <c r="A66" t="s">
         <v>645</v>
       </c>
@@ -10077,7 +10083,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="67" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:39" hidden="1">
       <c r="A67" t="s">
         <v>645</v>
       </c>
@@ -10178,7 +10184,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="68" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:39" hidden="1">
       <c r="A68" t="s">
         <v>651</v>
       </c>
@@ -10273,7 +10279,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="69" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:39" hidden="1">
       <c r="A69" t="s">
         <v>651</v>
       </c>
@@ -10368,7 +10374,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="70" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:39" hidden="1">
       <c r="A70" t="s">
         <v>656</v>
       </c>
@@ -10466,7 +10472,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="71" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:39" hidden="1">
       <c r="A71" t="s">
         <v>656</v>
       </c>
@@ -10564,7 +10570,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="72" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:39" hidden="1">
       <c r="A72" t="s">
         <v>656</v>
       </c>
@@ -10662,7 +10668,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="73" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:39" hidden="1">
       <c r="A73" t="s">
         <v>656</v>
       </c>
@@ -10760,7 +10766,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="74" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:39" hidden="1">
       <c r="A74" t="s">
         <v>179</v>
       </c>
@@ -10855,7 +10861,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="75" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:39" hidden="1">
       <c r="A75" t="s">
         <v>665</v>
       </c>
@@ -10953,7 +10959,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="76" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:39" hidden="1">
       <c r="A76" t="s">
         <v>669</v>
       </c>
@@ -11051,7 +11057,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="77" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:39" hidden="1">
       <c r="A77" t="s">
         <v>669</v>
       </c>
@@ -11149,7 +11155,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="78" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:39" hidden="1">
       <c r="A78" t="s">
         <v>673</v>
       </c>
@@ -11247,7 +11253,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="79" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:39" hidden="1">
       <c r="A79" t="s">
         <v>678</v>
       </c>
@@ -11345,7 +11351,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="80" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:39" hidden="1">
       <c r="A80" t="s">
         <v>678</v>
       </c>
@@ -11443,7 +11449,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="81" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:39" hidden="1">
       <c r="A81" t="s">
         <v>684</v>
       </c>
@@ -11541,7 +11547,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="82" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:39" hidden="1">
       <c r="A82" t="s">
         <v>690</v>
       </c>
@@ -11636,7 +11642,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="83" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:39" hidden="1">
       <c r="A83" t="s">
         <v>690</v>
       </c>
@@ -11731,7 +11737,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="84" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:39" hidden="1">
       <c r="A84" t="s">
         <v>185</v>
       </c>
@@ -11826,7 +11832,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="85" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:39" hidden="1">
       <c r="A85" t="s">
         <v>698</v>
       </c>
@@ -11924,7 +11930,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="86" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:39">
       <c r="A86" t="s">
         <v>704</v>
       </c>
@@ -12010,10 +12016,10 @@
         <v>257</v>
       </c>
       <c r="AJ86">
-        <v>38.255833000000003</v>
+        <v>38.256856999999997</v>
       </c>
       <c r="AK86">
-        <v>-104.675111</v>
+        <v>-104.576415</v>
       </c>
       <c r="AL86" t="s">
         <v>429</v>
@@ -12022,7 +12028,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="87" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:39" ht="23" hidden="1">
       <c r="A87" t="s">
         <v>708</v>
       </c>
@@ -12107,8 +12113,8 @@
       <c r="AJ87">
         <v>39.874093000000002</v>
       </c>
-      <c r="AK87">
-        <v>-104.91247</v>
+      <c r="AK87" s="3" t="s">
+        <v>1075</v>
       </c>
       <c r="AL87" t="s">
         <v>429</v>
@@ -12117,7 +12123,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="88" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:39" hidden="1">
       <c r="A88" t="s">
         <v>708</v>
       </c>
@@ -12212,7 +12218,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="89" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:39" hidden="1">
       <c r="A89" t="s">
         <v>713</v>
       </c>
@@ -12313,7 +12319,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="90" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:39" hidden="1">
       <c r="A90" t="s">
         <v>713</v>
       </c>
@@ -12414,7 +12420,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="91" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:39" hidden="1">
       <c r="A91" t="s">
         <v>720</v>
       </c>
@@ -12509,7 +12515,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="92" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:39" hidden="1">
       <c r="A92" t="s">
         <v>725</v>
       </c>
@@ -12607,7 +12613,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="93" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:39" hidden="1">
       <c r="A93" t="s">
         <v>731</v>
       </c>
@@ -12705,7 +12711,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="94" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:39" hidden="1">
       <c r="A94" t="s">
         <v>191</v>
       </c>
@@ -12806,7 +12812,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="95" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:39" hidden="1">
       <c r="A95" t="s">
         <v>198</v>
       </c>
@@ -12901,7 +12907,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="96" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:39" hidden="1">
       <c r="A96" t="s">
         <v>739</v>
       </c>
@@ -12996,7 +13002,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="97" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:39" hidden="1">
       <c r="A97" t="s">
         <v>743</v>
       </c>
@@ -13091,7 +13097,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="98" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:39" hidden="1">
       <c r="A98" t="s">
         <v>743</v>
       </c>
@@ -13186,7 +13192,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="99" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:39" hidden="1">
       <c r="A99" t="s">
         <v>204</v>
       </c>
@@ -13284,7 +13290,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="100" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:39" hidden="1">
       <c r="A100" t="s">
         <v>750</v>
       </c>
@@ -13379,7 +13385,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="101" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:39" hidden="1">
       <c r="A101" t="s">
         <v>210</v>
       </c>
@@ -13483,7 +13489,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="102" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:39" hidden="1">
       <c r="A102" t="s">
         <v>755</v>
       </c>
@@ -13578,7 +13584,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="103" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:39" hidden="1">
       <c r="A103" t="s">
         <v>218</v>
       </c>
@@ -13676,7 +13682,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="104" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:39" hidden="1">
       <c r="A104" t="s">
         <v>760</v>
       </c>
@@ -13774,7 +13780,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="105" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:39" hidden="1">
       <c r="A105" t="s">
         <v>224</v>
       </c>
@@ -13872,7 +13878,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:39" hidden="1">
       <c r="A106" t="s">
         <v>767</v>
       </c>
@@ -13967,7 +13973,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:39" hidden="1">
       <c r="A107" t="s">
         <v>230</v>
       </c>
@@ -14062,7 +14068,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:39" hidden="1">
       <c r="A108" t="s">
         <v>236</v>
       </c>
@@ -14160,7 +14166,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:39" hidden="1">
       <c r="A109" t="s">
         <v>774</v>
       </c>
@@ -14258,7 +14264,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:39" hidden="1">
       <c r="A110" t="s">
         <v>774</v>
       </c>
@@ -14356,7 +14362,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:39" hidden="1">
       <c r="A111" t="s">
         <v>774</v>
       </c>
@@ -14454,7 +14460,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:39" hidden="1">
       <c r="A112" t="s">
         <v>774</v>
       </c>
@@ -14552,7 +14558,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:39" hidden="1">
       <c r="A113" t="s">
         <v>774</v>
       </c>
@@ -14650,7 +14656,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:39" hidden="1">
       <c r="A114" t="s">
         <v>242</v>
       </c>
@@ -14748,7 +14754,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="115" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:39" hidden="1">
       <c r="A115" t="s">
         <v>781</v>
       </c>
@@ -14843,7 +14849,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="116" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:39" hidden="1">
       <c r="A116" t="s">
         <v>787</v>
       </c>
@@ -14941,7 +14947,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="117" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:39" hidden="1">
       <c r="A117" t="s">
         <v>791</v>
       </c>
@@ -15039,7 +15045,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:39" hidden="1">
       <c r="A118" t="s">
         <v>797</v>
       </c>
@@ -15134,7 +15140,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:39" hidden="1">
       <c r="A119" t="s">
         <v>803</v>
       </c>
@@ -15232,7 +15238,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:39" hidden="1">
       <c r="A120" t="s">
         <v>809</v>
       </c>
@@ -15327,7 +15333,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:39" hidden="1">
       <c r="A121" t="s">
         <v>815</v>
       </c>
@@ -15425,7 +15431,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:39" hidden="1">
       <c r="A122" t="s">
         <v>246</v>
       </c>
@@ -15520,7 +15526,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:39" hidden="1">
       <c r="A123" t="s">
         <v>820</v>
       </c>
@@ -15618,7 +15624,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:39" hidden="1">
       <c r="A124" t="s">
         <v>251</v>
       </c>
@@ -15713,7 +15719,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:39" hidden="1">
       <c r="A125" t="s">
         <v>251</v>
       </c>
@@ -15808,7 +15814,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:39" hidden="1">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -15903,7 +15909,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:39" hidden="1">
       <c r="A127" t="s">
         <v>251</v>
       </c>
@@ -15998,7 +16004,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:39" hidden="1">
       <c r="A128" t="s">
         <v>826</v>
       </c>
@@ -16096,7 +16102,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:39" hidden="1">
       <c r="A129" t="s">
         <v>826</v>
       </c>
@@ -16194,7 +16200,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:39" hidden="1">
       <c r="A130" t="s">
         <v>833</v>
       </c>
@@ -16289,7 +16295,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:39" hidden="1">
       <c r="A131" t="s">
         <v>839</v>
       </c>
@@ -16387,7 +16393,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:39" hidden="1">
       <c r="A132" t="s">
         <v>839</v>
       </c>
@@ -16485,7 +16491,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:39" hidden="1">
       <c r="A133" t="s">
         <v>258</v>
       </c>
@@ -16583,7 +16589,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:39" hidden="1">
       <c r="A134" t="s">
         <v>846</v>
       </c>
@@ -16678,7 +16684,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:39" hidden="1">
       <c r="A135" t="s">
         <v>850</v>
       </c>
@@ -16776,7 +16782,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:39" hidden="1">
       <c r="A136" t="s">
         <v>850</v>
       </c>
@@ -16874,7 +16880,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:39" hidden="1">
       <c r="A137" t="s">
         <v>850</v>
       </c>
@@ -16972,7 +16978,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:39" hidden="1">
       <c r="A138" t="s">
         <v>850</v>
       </c>
@@ -17070,7 +17076,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="139" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:39" hidden="1">
       <c r="A139" t="s">
         <v>856</v>
       </c>
@@ -17168,7 +17174,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="140" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:39" hidden="1">
       <c r="A140" t="s">
         <v>856</v>
       </c>
@@ -17266,7 +17272,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="141" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:39" hidden="1">
       <c r="A141" t="s">
         <v>860</v>
       </c>
@@ -17364,7 +17370,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="142" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:39" hidden="1">
       <c r="A142" t="s">
         <v>264</v>
       </c>
@@ -17459,7 +17465,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="143" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:39" hidden="1">
       <c r="A143" t="s">
         <v>269</v>
       </c>
@@ -17560,7 +17566,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="144" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:39" hidden="1">
       <c r="A144" t="s">
         <v>269</v>
       </c>
@@ -17661,7 +17667,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="145" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:39" hidden="1">
       <c r="A145" t="s">
         <v>269</v>
       </c>
@@ -17762,7 +17768,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="146" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:39" hidden="1">
       <c r="A146" t="s">
         <v>868</v>
       </c>
@@ -17860,7 +17866,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="147" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:39" hidden="1">
       <c r="A147" t="s">
         <v>874</v>
       </c>
@@ -17958,7 +17964,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="148" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:39" hidden="1">
       <c r="A148" t="s">
         <v>880</v>
       </c>
@@ -18056,7 +18062,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="149" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:39" hidden="1">
       <c r="A149" t="s">
         <v>274</v>
       </c>
@@ -18157,7 +18163,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="150" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:39" hidden="1">
       <c r="A150" t="s">
         <v>274</v>
       </c>
@@ -18258,7 +18264,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="151" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:39" hidden="1">
       <c r="A151" t="s">
         <v>274</v>
       </c>
@@ -18359,7 +18365,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="152" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:39" hidden="1">
       <c r="A152" t="s">
         <v>279</v>
       </c>
@@ -18457,7 +18463,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="153" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:39" hidden="1">
       <c r="A153" t="s">
         <v>284</v>
       </c>
@@ -18552,7 +18558,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="154" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:39" hidden="1">
       <c r="A154" t="s">
         <v>289</v>
       </c>
@@ -18656,7 +18662,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="155" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:39" hidden="1">
       <c r="A155" t="s">
         <v>887</v>
       </c>
@@ -18754,7 +18760,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="156" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:39" hidden="1">
       <c r="A156" t="s">
         <v>296</v>
       </c>
@@ -18849,7 +18855,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="157" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:39" hidden="1">
       <c r="A157" t="s">
         <v>296</v>
       </c>
@@ -18944,7 +18950,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="158" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:39" hidden="1">
       <c r="A158" t="s">
         <v>891</v>
       </c>
@@ -19042,7 +19048,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="159" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:39" hidden="1">
       <c r="A159" t="s">
         <v>302</v>
       </c>
@@ -19143,7 +19149,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="160" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:39" hidden="1">
       <c r="A160" t="s">
         <v>898</v>
       </c>
@@ -19238,7 +19244,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="161" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:39" hidden="1">
       <c r="A161" t="s">
         <v>898</v>
       </c>
@@ -19333,7 +19339,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="162" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:39" hidden="1">
       <c r="A162" t="s">
         <v>903</v>
       </c>
@@ -19428,7 +19434,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="163" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:39" hidden="1">
       <c r="A163" t="s">
         <v>907</v>
       </c>
@@ -19523,7 +19529,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="164" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:39" hidden="1">
       <c r="A164" t="s">
         <v>307</v>
       </c>
@@ -19618,7 +19624,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="165" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:39" hidden="1">
       <c r="A165" t="s">
         <v>307</v>
       </c>
@@ -19713,7 +19719,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="166" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:39" hidden="1">
       <c r="A166" t="s">
         <v>313</v>
       </c>
@@ -19811,7 +19817,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="167" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:39" hidden="1">
       <c r="A167" t="s">
         <v>915</v>
       </c>
@@ -19909,7 +19915,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="168" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:39" hidden="1">
       <c r="A168" t="s">
         <v>319</v>
       </c>
@@ -20004,7 +20010,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="169" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:39" hidden="1">
       <c r="A169" t="s">
         <v>919</v>
       </c>
@@ -20102,7 +20108,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="170" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:39" hidden="1">
       <c r="A170" t="s">
         <v>925</v>
       </c>
@@ -20197,7 +20203,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="171" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:39" hidden="1">
       <c r="A171" t="s">
         <v>324</v>
       </c>
@@ -20292,7 +20298,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="172" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:39" hidden="1">
       <c r="A172" t="s">
         <v>329</v>
       </c>
@@ -20387,7 +20393,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="173" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:39" hidden="1">
       <c r="A173" t="s">
         <v>329</v>
       </c>
@@ -20482,7 +20488,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="174" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:39" hidden="1">
       <c r="A174" t="s">
         <v>334</v>
       </c>
@@ -20580,7 +20586,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="175" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:39" hidden="1">
       <c r="A175" t="s">
         <v>933</v>
       </c>
@@ -20678,7 +20684,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="176" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:39" hidden="1">
       <c r="A176" t="s">
         <v>937</v>
       </c>
@@ -20776,7 +20782,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="177" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:39" hidden="1">
       <c r="A177" t="s">
         <v>937</v>
       </c>
@@ -20874,7 +20880,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="178" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:39" hidden="1">
       <c r="A178" t="s">
         <v>339</v>
       </c>
@@ -20969,7 +20975,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="179" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:39" hidden="1">
       <c r="A179" t="s">
         <v>345</v>
       </c>
@@ -21064,7 +21070,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="180" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:39" hidden="1">
       <c r="A180" t="s">
         <v>345</v>
       </c>
@@ -21159,7 +21165,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="181" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:39" hidden="1">
       <c r="A181" t="s">
         <v>345</v>
       </c>
@@ -21254,7 +21260,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="182" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:39" hidden="1">
       <c r="A182" t="s">
         <v>944</v>
       </c>
@@ -21352,7 +21358,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="183" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:39" hidden="1">
       <c r="A183" t="s">
         <v>350</v>
       </c>
@@ -21450,7 +21456,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="184" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:39" hidden="1">
       <c r="A184" t="s">
         <v>949</v>
       </c>
@@ -21545,7 +21551,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="185" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:39" hidden="1">
       <c r="A185" t="s">
         <v>953</v>
       </c>
@@ -21640,7 +21646,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="186" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:39" hidden="1">
       <c r="A186" t="s">
         <v>355</v>
       </c>
@@ -21735,7 +21741,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="187" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:39" hidden="1">
       <c r="A187" t="s">
         <v>959</v>
       </c>
@@ -21830,7 +21836,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="188" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:39" hidden="1">
       <c r="A188" t="s">
         <v>965</v>
       </c>
@@ -21925,7 +21931,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="189" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:39" hidden="1">
       <c r="A189" t="s">
         <v>971</v>
       </c>
@@ -22023,7 +22029,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="190" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:39" hidden="1">
       <c r="A190" t="s">
         <v>971</v>
       </c>
@@ -22121,7 +22127,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="191" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:39" hidden="1">
       <c r="A191" t="s">
         <v>360</v>
       </c>
@@ -22216,7 +22222,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="192" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:39" hidden="1">
       <c r="A192" t="s">
         <v>977</v>
       </c>
@@ -22311,7 +22317,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="193" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:39" hidden="1">
       <c r="A193" t="s">
         <v>366</v>
       </c>
@@ -22409,7 +22415,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="194" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:39" hidden="1">
       <c r="A194" t="s">
         <v>372</v>
       </c>
@@ -22504,7 +22510,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="195" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:39" hidden="1">
       <c r="A195" t="s">
         <v>982</v>
       </c>
@@ -22599,7 +22605,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="196" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:39" hidden="1">
       <c r="A196" t="s">
         <v>985</v>
       </c>
@@ -22694,7 +22700,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="197" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:39" hidden="1">
       <c r="A197" t="s">
         <v>990</v>
       </c>
@@ -22789,7 +22795,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="198" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:39" hidden="1">
       <c r="A198" t="s">
         <v>995</v>
       </c>
@@ -22887,7 +22893,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="199" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:39" hidden="1">
       <c r="A199" t="s">
         <v>378</v>
       </c>
@@ -22985,7 +22991,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="200" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:39" hidden="1">
       <c r="A200" t="s">
         <v>1000</v>
       </c>
@@ -23080,7 +23086,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="201" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:39" hidden="1">
       <c r="A201" t="s">
         <v>1005</v>
       </c>
@@ -23178,7 +23184,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="202" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:39" hidden="1">
       <c r="A202" t="s">
         <v>1011</v>
       </c>
@@ -23273,7 +23279,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="203" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:39" hidden="1">
       <c r="A203" t="s">
         <v>1015</v>
       </c>
@@ -23368,7 +23374,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="204" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:39" hidden="1">
       <c r="A204" t="s">
         <v>384</v>
       </c>
@@ -23466,7 +23472,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="205" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:39" hidden="1">
       <c r="A205" t="s">
         <v>1020</v>
       </c>
@@ -23564,7 +23570,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="206" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:39" hidden="1">
       <c r="A206" t="s">
         <v>1020</v>
       </c>
@@ -23662,7 +23668,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="207" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:39" hidden="1">
       <c r="A207" t="s">
         <v>390</v>
       </c>
@@ -23757,7 +23763,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="208" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:39" hidden="1">
       <c r="A208" t="s">
         <v>1025</v>
       </c>
@@ -23852,7 +23858,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="209" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:39" hidden="1">
       <c r="A209" t="s">
         <v>395</v>
       </c>
@@ -23950,7 +23956,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="210" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:39" hidden="1">
       <c r="A210" t="s">
         <v>400</v>
       </c>
@@ -24048,7 +24054,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="211" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:39" hidden="1">
       <c r="A211" t="s">
         <v>1030</v>
       </c>
@@ -24146,7 +24152,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="212" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:39" hidden="1">
       <c r="A212" t="s">
         <v>1030</v>
       </c>
@@ -24244,7 +24250,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="213" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:39" hidden="1">
       <c r="A213" t="s">
         <v>1037</v>
       </c>
@@ -24339,7 +24345,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="214" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:39" hidden="1">
       <c r="A214" t="s">
         <v>1037</v>
       </c>
@@ -24434,7 +24440,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="215" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:39" hidden="1">
       <c r="A215" t="s">
         <v>1043</v>
       </c>
@@ -24529,7 +24535,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="216" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:39" hidden="1">
       <c r="A216" t="s">
         <v>1047</v>
       </c>
@@ -24624,7 +24630,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="217" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:39" hidden="1">
       <c r="A217" t="s">
         <v>1052</v>
       </c>
@@ -24722,7 +24728,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="218" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:39" hidden="1">
       <c r="A218" t="s">
         <v>405</v>
       </c>
@@ -24820,7 +24826,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="219" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:39" hidden="1">
       <c r="A219" t="s">
         <v>1059</v>
       </c>
@@ -24915,7 +24921,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="220" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:39" hidden="1">
       <c r="A220" t="s">
         <v>411</v>
       </c>
@@ -25010,7 +25016,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="221" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:39" hidden="1">
       <c r="A221" t="s">
         <v>418</v>
       </c>
@@ -25111,7 +25117,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="222" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:39" hidden="1">
       <c r="A222" t="s">
         <v>1066</v>
       </c>
@@ -25209,7 +25215,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="223" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:39" hidden="1">
       <c r="A223" t="s">
         <v>1071</v>
       </c>
@@ -25268,11 +25274,17 @@
         <v>430</v>
       </c>
     </row>
-    <row r="251" spans="25:25" x14ac:dyDescent="0.2">
+    <row r="251" spans="25:25">
       <c r="Y251" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM223" xr:uid="{87B7DC3E-A36C-1846-B0DD-7107AEF1D1CD}"/>
+  <autoFilter ref="A1:AM223" xr:uid="{87B7DC3E-A36C-1846-B0DD-7107AEF1D1CD}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="JAMES R DIIORIO WATER RECLAMATION FAC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -25289,6 +25301,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D9006C60258807429405E6C73BA3CCFE" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="137f2adf86c334d9e1e126da1ac5c085">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3078a4d3-167c-42ae-9b46-6e3db872b3ec" xmlns:ns3="4d95fb05-5706-4269-8c5d-48c42636077e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b6835ff1cba96eec22b1ba4ba43253d8" ns2:_="" ns3:_="">
     <xsd:import namespace="3078a4d3-167c-42ae-9b46-6e3db872b3ec"/>
@@ -25529,15 +25550,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A35900C-E0AD-40CC-BC89-8EB93FFF6CB2}">
   <ds:schemaRefs>
@@ -25556,6 +25568,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E5BC3AB-2CCE-499F-B8C2-1C0387FD3409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EECD754-9407-4618-AE41-D9F21446A5DF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25574,14 +25594,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E5BC3AB-2CCE-499F-B8C2-1C0387FD3409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3ded8b1b-070d-4629-82e4-c0b019f46057}" enabled="0" method="" siteId="{3ded8b1b-070d-4629-82e4-c0b019f46057}" removed="1"/>

--- a/ReSourceTracker/data-raw/PermittedPOTW.xlsx
+++ b/ReSourceTracker/data-raw/PermittedPOTW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kylieboenischoakes/Documents/ResourceTracker/ReSourceTracker/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4D0416-91AB-254C-85B2-BC4BE8B498E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141C0217-4003-B245-A8DC-51A58DAAFFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{1EFE79D8-E86D-494B-8A17-9BCECD28B3B3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4979" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="1075">
   <si>
     <t>EXTERNAL_PERMIT_NMBR</t>
   </si>
@@ -3264,16 +3264,13 @@
   </si>
   <si>
     <t>BOULDER CREEK</t>
-  </si>
-  <si>
-    <t></t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3289,9 +3286,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Google Symbols"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3653,14 +3651,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B7DC3E-A36C-1846-B0DD-7107AEF1D1CD}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AM251"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="17" max="17" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3779,7 +3776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" hidden="1">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>423</v>
       </c>
@@ -3874,7 +3871,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="3" spans="1:39" hidden="1">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>423</v>
       </c>
@@ -3969,7 +3966,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" spans="1:39" hidden="1">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>431</v>
       </c>
@@ -4064,7 +4061,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="5" spans="1:39" hidden="1">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>437</v>
       </c>
@@ -4162,7 +4159,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="6" spans="1:39" hidden="1">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -4260,7 +4257,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="7" spans="1:39" hidden="1">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -4358,7 +4355,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="8" spans="1:39" hidden="1">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>447</v>
       </c>
@@ -4456,7 +4453,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="9" spans="1:39" hidden="1">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>454</v>
       </c>
@@ -4557,7 +4554,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="1:39" hidden="1">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>460</v>
       </c>
@@ -4655,7 +4652,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="11" spans="1:39" hidden="1">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -4756,7 +4753,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="12" spans="1:39" hidden="1">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>466</v>
       </c>
@@ -4854,7 +4851,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:39" hidden="1">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -4949,7 +4946,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" spans="1:39" hidden="1">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -5044,7 +5041,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="15" spans="1:39" hidden="1">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>475</v>
       </c>
@@ -5139,7 +5136,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="16" spans="1:39" hidden="1">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>481</v>
       </c>
@@ -5237,7 +5234,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="17" spans="1:39" hidden="1">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>487</v>
       </c>
@@ -5335,7 +5332,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="1:39" hidden="1">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>492</v>
       </c>
@@ -5430,7 +5427,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="19" spans="1:39" hidden="1">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>496</v>
       </c>
@@ -5528,7 +5525,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:39" hidden="1">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>500</v>
       </c>
@@ -5626,7 +5623,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="21" spans="1:39" hidden="1">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>507</v>
       </c>
@@ -5724,7 +5721,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="22" spans="1:39" hidden="1">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>512</v>
       </c>
@@ -5822,7 +5819,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="23" spans="1:39" hidden="1">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>517</v>
       </c>
@@ -5917,7 +5914,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="24" spans="1:39" hidden="1">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>524</v>
       </c>
@@ -6012,7 +6009,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="25" spans="1:39" hidden="1">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>524</v>
       </c>
@@ -6107,7 +6104,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="26" spans="1:39" hidden="1">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>524</v>
       </c>
@@ -6202,7 +6199,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="27" spans="1:39" hidden="1">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>532</v>
       </c>
@@ -6297,7 +6294,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="28" spans="1:39" hidden="1">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -6392,7 +6389,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="29" spans="1:39" hidden="1">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -6487,7 +6484,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="30" spans="1:39" hidden="1">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>98</v>
       </c>
@@ -6582,7 +6579,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="31" spans="1:39" hidden="1">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>539</v>
       </c>
@@ -6680,7 +6677,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="32" spans="1:39" hidden="1">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -6778,7 +6775,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="33" spans="1:39" hidden="1">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>109</v>
       </c>
@@ -6876,7 +6873,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:39" hidden="1">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>546</v>
       </c>
@@ -6974,7 +6971,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="35" spans="1:39" hidden="1">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>552</v>
       </c>
@@ -7072,7 +7069,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="36" spans="1:39" hidden="1">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -7170,7 +7167,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="37" spans="1:39" hidden="1">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>124</v>
       </c>
@@ -7265,7 +7262,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="38" spans="1:39" hidden="1">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>557</v>
       </c>
@@ -7360,7 +7357,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="39" spans="1:39" hidden="1">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>557</v>
       </c>
@@ -7455,7 +7452,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="40" spans="1:39" hidden="1">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>557</v>
       </c>
@@ -7550,7 +7547,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:39" hidden="1">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>564</v>
       </c>
@@ -7648,7 +7645,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="42" spans="1:39" hidden="1">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>130</v>
       </c>
@@ -7746,7 +7743,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="43" spans="1:39" hidden="1">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>571</v>
       </c>
@@ -7844,7 +7841,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="44" spans="1:39" hidden="1">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>576</v>
       </c>
@@ -7939,7 +7936,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="45" spans="1:39" hidden="1">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>580</v>
       </c>
@@ -8037,7 +8034,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="46" spans="1:39" hidden="1">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>137</v>
       </c>
@@ -8132,7 +8129,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="47" spans="1:39" hidden="1">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -8233,7 +8230,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="48" spans="1:39" hidden="1">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -8328,7 +8325,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="49" spans="1:39" hidden="1">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>157</v>
       </c>
@@ -8423,7 +8420,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="50" spans="1:39" hidden="1">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>587</v>
       </c>
@@ -8518,7 +8515,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="51" spans="1:39" hidden="1">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>591</v>
       </c>
@@ -8613,7 +8610,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="52" spans="1:39" hidden="1">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>596</v>
       </c>
@@ -8711,7 +8708,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="53" spans="1:39" hidden="1">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>601</v>
       </c>
@@ -8806,7 +8803,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="54" spans="1:39" hidden="1">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>607</v>
       </c>
@@ -8904,7 +8901,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="55" spans="1:39" hidden="1">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>613</v>
       </c>
@@ -8999,7 +8996,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="56" spans="1:39" hidden="1">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>613</v>
       </c>
@@ -9094,7 +9091,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="57" spans="1:39" hidden="1">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>620</v>
       </c>
@@ -9195,7 +9192,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="58" spans="1:39" hidden="1">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>620</v>
       </c>
@@ -9296,7 +9293,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="59" spans="1:39" hidden="1">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>620</v>
       </c>
@@ -9397,7 +9394,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="60" spans="1:39" hidden="1">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>628</v>
       </c>
@@ -9492,7 +9489,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="61" spans="1:39" hidden="1">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>162</v>
       </c>
@@ -9593,7 +9590,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="62" spans="1:39" hidden="1">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>168</v>
       </c>
@@ -9691,7 +9688,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="63" spans="1:39" hidden="1">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>633</v>
       </c>
@@ -9789,7 +9786,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="64" spans="1:39" hidden="1">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>173</v>
       </c>
@@ -9887,7 +9884,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="65" spans="1:39" hidden="1">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>640</v>
       </c>
@@ -9985,7 +9982,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="66" spans="1:39" hidden="1">
+    <row r="66" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>645</v>
       </c>
@@ -10083,7 +10080,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="67" spans="1:39" hidden="1">
+    <row r="67" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>645</v>
       </c>
@@ -10184,7 +10181,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="68" spans="1:39" hidden="1">
+    <row r="68" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>651</v>
       </c>
@@ -10279,7 +10276,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="69" spans="1:39" hidden="1">
+    <row r="69" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>651</v>
       </c>
@@ -10374,7 +10371,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="70" spans="1:39" hidden="1">
+    <row r="70" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>656</v>
       </c>
@@ -10472,7 +10469,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="71" spans="1:39" hidden="1">
+    <row r="71" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>656</v>
       </c>
@@ -10570,7 +10567,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="72" spans="1:39" hidden="1">
+    <row r="72" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>656</v>
       </c>
@@ -10668,7 +10665,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="73" spans="1:39" hidden="1">
+    <row r="73" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>656</v>
       </c>
@@ -10766,7 +10763,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="74" spans="1:39" hidden="1">
+    <row r="74" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>179</v>
       </c>
@@ -10861,7 +10858,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="75" spans="1:39" hidden="1">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>665</v>
       </c>
@@ -10959,7 +10956,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="76" spans="1:39" hidden="1">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>669</v>
       </c>
@@ -11057,7 +11054,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="77" spans="1:39" hidden="1">
+    <row r="77" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>669</v>
       </c>
@@ -11155,7 +11152,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="78" spans="1:39" hidden="1">
+    <row r="78" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>673</v>
       </c>
@@ -11253,7 +11250,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="79" spans="1:39" hidden="1">
+    <row r="79" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>678</v>
       </c>
@@ -11351,7 +11348,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="80" spans="1:39" hidden="1">
+    <row r="80" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>678</v>
       </c>
@@ -11449,7 +11446,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="81" spans="1:39" hidden="1">
+    <row r="81" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>684</v>
       </c>
@@ -11547,7 +11544,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="82" spans="1:39" hidden="1">
+    <row r="82" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>690</v>
       </c>
@@ -11642,7 +11639,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="83" spans="1:39" hidden="1">
+    <row r="83" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>690</v>
       </c>
@@ -11737,7 +11734,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="84" spans="1:39" hidden="1">
+    <row r="84" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>185</v>
       </c>
@@ -11832,7 +11829,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="85" spans="1:39" hidden="1">
+    <row r="85" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>698</v>
       </c>
@@ -11930,7 +11927,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="86" spans="1:39">
+    <row r="86" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>704</v>
       </c>
@@ -12028,7 +12025,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="87" spans="1:39" ht="23" hidden="1">
+    <row r="87" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>708</v>
       </c>
@@ -12110,11 +12107,11 @@
       <c r="AI87" t="s">
         <v>545</v>
       </c>
-      <c r="AJ87">
+      <c r="AJ87" s="3">
         <v>39.874093000000002</v>
       </c>
-      <c r="AK87" s="3" t="s">
-        <v>1075</v>
+      <c r="AK87" s="3">
+        <v>-104.91247</v>
       </c>
       <c r="AL87" t="s">
         <v>429</v>
@@ -12123,7 +12120,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="88" spans="1:39" hidden="1">
+    <row r="88" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>708</v>
       </c>
@@ -12218,7 +12215,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="89" spans="1:39" hidden="1">
+    <row r="89" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>713</v>
       </c>
@@ -12319,7 +12316,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="90" spans="1:39" hidden="1">
+    <row r="90" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>713</v>
       </c>
@@ -12420,7 +12417,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="91" spans="1:39" hidden="1">
+    <row r="91" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>720</v>
       </c>
@@ -12515,7 +12512,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="92" spans="1:39" hidden="1">
+    <row r="92" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>725</v>
       </c>
@@ -12613,7 +12610,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="93" spans="1:39" hidden="1">
+    <row r="93" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>731</v>
       </c>
@@ -12711,7 +12708,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="94" spans="1:39" hidden="1">
+    <row r="94" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>191</v>
       </c>
@@ -12812,7 +12809,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="95" spans="1:39" hidden="1">
+    <row r="95" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>198</v>
       </c>
@@ -12907,7 +12904,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="96" spans="1:39" hidden="1">
+    <row r="96" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>739</v>
       </c>
@@ -13002,7 +12999,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="97" spans="1:39" hidden="1">
+    <row r="97" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>743</v>
       </c>
@@ -13097,7 +13094,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="98" spans="1:39" hidden="1">
+    <row r="98" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>743</v>
       </c>
@@ -13192,7 +13189,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="99" spans="1:39" hidden="1">
+    <row r="99" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>204</v>
       </c>
@@ -13290,7 +13287,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="100" spans="1:39" hidden="1">
+    <row r="100" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>750</v>
       </c>
@@ -13385,7 +13382,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="101" spans="1:39" hidden="1">
+    <row r="101" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>210</v>
       </c>
@@ -13489,7 +13486,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="102" spans="1:39" hidden="1">
+    <row r="102" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>755</v>
       </c>
@@ -13584,7 +13581,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="103" spans="1:39" hidden="1">
+    <row r="103" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>218</v>
       </c>
@@ -13682,7 +13679,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="104" spans="1:39" hidden="1">
+    <row r="104" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>760</v>
       </c>
@@ -13780,7 +13777,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="105" spans="1:39" hidden="1">
+    <row r="105" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>224</v>
       </c>
@@ -13878,7 +13875,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="106" spans="1:39" hidden="1">
+    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>767</v>
       </c>
@@ -13973,7 +13970,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="107" spans="1:39" hidden="1">
+    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>230</v>
       </c>
@@ -14068,7 +14065,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="108" spans="1:39" hidden="1">
+    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>236</v>
       </c>
@@ -14166,7 +14163,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="109" spans="1:39" hidden="1">
+    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>774</v>
       </c>
@@ -14264,7 +14261,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="110" spans="1:39" hidden="1">
+    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>774</v>
       </c>
@@ -14362,7 +14359,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="111" spans="1:39" hidden="1">
+    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>774</v>
       </c>
@@ -14460,7 +14457,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="112" spans="1:39" hidden="1">
+    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>774</v>
       </c>
@@ -14558,7 +14555,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="113" spans="1:39" hidden="1">
+    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>774</v>
       </c>
@@ -14656,7 +14653,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="114" spans="1:39" hidden="1">
+    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>242</v>
       </c>
@@ -14754,7 +14751,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="115" spans="1:39" hidden="1">
+    <row r="115" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>781</v>
       </c>
@@ -14849,7 +14846,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="116" spans="1:39" hidden="1">
+    <row r="116" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>787</v>
       </c>
@@ -14947,7 +14944,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="117" spans="1:39" hidden="1">
+    <row r="117" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>791</v>
       </c>
@@ -15045,7 +15042,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="118" spans="1:39" hidden="1">
+    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>797</v>
       </c>
@@ -15140,7 +15137,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="119" spans="1:39" hidden="1">
+    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>803</v>
       </c>
@@ -15238,7 +15235,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="120" spans="1:39" hidden="1">
+    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>809</v>
       </c>
@@ -15333,7 +15330,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="121" spans="1:39" hidden="1">
+    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>815</v>
       </c>
@@ -15431,7 +15428,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="122" spans="1:39" hidden="1">
+    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>246</v>
       </c>
@@ -15526,7 +15523,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="123" spans="1:39" hidden="1">
+    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>820</v>
       </c>
@@ -15624,7 +15621,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="124" spans="1:39" hidden="1">
+    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>251</v>
       </c>
@@ -15719,7 +15716,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="125" spans="1:39" hidden="1">
+    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>251</v>
       </c>
@@ -15814,7 +15811,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="126" spans="1:39" hidden="1">
+    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -15909,7 +15906,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="127" spans="1:39" hidden="1">
+    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>251</v>
       </c>
@@ -16004,7 +16001,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="128" spans="1:39" hidden="1">
+    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>826</v>
       </c>
@@ -16102,7 +16099,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="129" spans="1:39" hidden="1">
+    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>826</v>
       </c>
@@ -16200,7 +16197,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="130" spans="1:39" hidden="1">
+    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>833</v>
       </c>
@@ -16295,7 +16292,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="131" spans="1:39" hidden="1">
+    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>839</v>
       </c>
@@ -16393,7 +16390,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="132" spans="1:39" hidden="1">
+    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>839</v>
       </c>
@@ -16491,7 +16488,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="133" spans="1:39" hidden="1">
+    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>258</v>
       </c>
@@ -16589,7 +16586,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="134" spans="1:39" hidden="1">
+    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>846</v>
       </c>
@@ -16684,7 +16681,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="135" spans="1:39" hidden="1">
+    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>850</v>
       </c>
@@ -16782,7 +16779,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="136" spans="1:39" hidden="1">
+    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>850</v>
       </c>
@@ -16880,7 +16877,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="137" spans="1:39" hidden="1">
+    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>850</v>
       </c>
@@ -16978,7 +16975,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="138" spans="1:39" hidden="1">
+    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>850</v>
       </c>
@@ -17076,7 +17073,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="139" spans="1:39" hidden="1">
+    <row r="139" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>856</v>
       </c>
@@ -17174,7 +17171,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="140" spans="1:39" hidden="1">
+    <row r="140" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>856</v>
       </c>
@@ -17272,7 +17269,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="141" spans="1:39" hidden="1">
+    <row r="141" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>860</v>
       </c>
@@ -17370,7 +17367,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="142" spans="1:39" hidden="1">
+    <row r="142" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>264</v>
       </c>
@@ -17465,7 +17462,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="143" spans="1:39" hidden="1">
+    <row r="143" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>269</v>
       </c>
@@ -17566,7 +17563,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="144" spans="1:39" hidden="1">
+    <row r="144" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>269</v>
       </c>
@@ -17667,7 +17664,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="145" spans="1:39" hidden="1">
+    <row r="145" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>269</v>
       </c>
@@ -17768,7 +17765,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="146" spans="1:39" hidden="1">
+    <row r="146" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>868</v>
       </c>
@@ -17866,7 +17863,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="147" spans="1:39" hidden="1">
+    <row r="147" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>874</v>
       </c>
@@ -17964,7 +17961,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="148" spans="1:39" hidden="1">
+    <row r="148" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>880</v>
       </c>
@@ -18062,7 +18059,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="149" spans="1:39" hidden="1">
+    <row r="149" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>274</v>
       </c>
@@ -18163,7 +18160,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="150" spans="1:39" hidden="1">
+    <row r="150" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>274</v>
       </c>
@@ -18264,7 +18261,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="151" spans="1:39" hidden="1">
+    <row r="151" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>274</v>
       </c>
@@ -18365,7 +18362,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="152" spans="1:39" hidden="1">
+    <row r="152" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>279</v>
       </c>
@@ -18463,7 +18460,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="153" spans="1:39" hidden="1">
+    <row r="153" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>284</v>
       </c>
@@ -18558,7 +18555,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="154" spans="1:39" hidden="1">
+    <row r="154" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>289</v>
       </c>
@@ -18662,7 +18659,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="155" spans="1:39" hidden="1">
+    <row r="155" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>887</v>
       </c>
@@ -18760,7 +18757,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="156" spans="1:39" hidden="1">
+    <row r="156" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>296</v>
       </c>
@@ -18855,7 +18852,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="157" spans="1:39" hidden="1">
+    <row r="157" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>296</v>
       </c>
@@ -18950,7 +18947,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="158" spans="1:39" hidden="1">
+    <row r="158" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>891</v>
       </c>
@@ -19048,7 +19045,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="159" spans="1:39" hidden="1">
+    <row r="159" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>302</v>
       </c>
@@ -19149,7 +19146,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="160" spans="1:39" hidden="1">
+    <row r="160" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>898</v>
       </c>
@@ -19244,7 +19241,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="161" spans="1:39" hidden="1">
+    <row r="161" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>898</v>
       </c>
@@ -19339,7 +19336,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="162" spans="1:39" hidden="1">
+    <row r="162" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>903</v>
       </c>
@@ -19434,7 +19431,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="163" spans="1:39" hidden="1">
+    <row r="163" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>907</v>
       </c>
@@ -19529,7 +19526,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="164" spans="1:39" hidden="1">
+    <row r="164" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>307</v>
       </c>
@@ -19624,7 +19621,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="165" spans="1:39" hidden="1">
+    <row r="165" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>307</v>
       </c>
@@ -19719,7 +19716,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="166" spans="1:39" hidden="1">
+    <row r="166" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>313</v>
       </c>
@@ -19817,7 +19814,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="167" spans="1:39" hidden="1">
+    <row r="167" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>915</v>
       </c>
@@ -19915,7 +19912,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="168" spans="1:39" hidden="1">
+    <row r="168" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>319</v>
       </c>
@@ -20010,7 +20007,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="169" spans="1:39" hidden="1">
+    <row r="169" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>919</v>
       </c>
@@ -20108,7 +20105,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="170" spans="1:39" hidden="1">
+    <row r="170" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>925</v>
       </c>
@@ -20203,7 +20200,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="171" spans="1:39" hidden="1">
+    <row r="171" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>324</v>
       </c>
@@ -20298,7 +20295,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="172" spans="1:39" hidden="1">
+    <row r="172" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>329</v>
       </c>
@@ -20393,7 +20390,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="173" spans="1:39" hidden="1">
+    <row r="173" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>329</v>
       </c>
@@ -20488,7 +20485,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="174" spans="1:39" hidden="1">
+    <row r="174" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>334</v>
       </c>
@@ -20586,7 +20583,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="175" spans="1:39" hidden="1">
+    <row r="175" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>933</v>
       </c>
@@ -20684,7 +20681,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="176" spans="1:39" hidden="1">
+    <row r="176" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>937</v>
       </c>
@@ -20782,7 +20779,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="177" spans="1:39" hidden="1">
+    <row r="177" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>937</v>
       </c>
@@ -20880,7 +20877,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="178" spans="1:39" hidden="1">
+    <row r="178" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>339</v>
       </c>
@@ -20975,7 +20972,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="179" spans="1:39" hidden="1">
+    <row r="179" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>345</v>
       </c>
@@ -21070,7 +21067,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="180" spans="1:39" hidden="1">
+    <row r="180" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>345</v>
       </c>
@@ -21165,7 +21162,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="181" spans="1:39" hidden="1">
+    <row r="181" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>345</v>
       </c>
@@ -21260,7 +21257,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="182" spans="1:39" hidden="1">
+    <row r="182" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>944</v>
       </c>
@@ -21358,7 +21355,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="183" spans="1:39" hidden="1">
+    <row r="183" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>350</v>
       </c>
@@ -21456,7 +21453,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="184" spans="1:39" hidden="1">
+    <row r="184" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>949</v>
       </c>
@@ -21551,7 +21548,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="185" spans="1:39" hidden="1">
+    <row r="185" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>953</v>
       </c>
@@ -21646,7 +21643,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="186" spans="1:39" hidden="1">
+    <row r="186" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>355</v>
       </c>
@@ -21741,7 +21738,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="187" spans="1:39" hidden="1">
+    <row r="187" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>959</v>
       </c>
@@ -21836,7 +21833,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="188" spans="1:39" hidden="1">
+    <row r="188" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>965</v>
       </c>
@@ -21931,7 +21928,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="189" spans="1:39" hidden="1">
+    <row r="189" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>971</v>
       </c>
@@ -22029,7 +22026,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="190" spans="1:39" hidden="1">
+    <row r="190" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>971</v>
       </c>
@@ -22127,7 +22124,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="191" spans="1:39" hidden="1">
+    <row r="191" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>360</v>
       </c>
@@ -22222,7 +22219,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="192" spans="1:39" hidden="1">
+    <row r="192" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>977</v>
       </c>
@@ -22317,7 +22314,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="193" spans="1:39" hidden="1">
+    <row r="193" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>366</v>
       </c>
@@ -22415,7 +22412,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="194" spans="1:39" hidden="1">
+    <row r="194" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>372</v>
       </c>
@@ -22510,7 +22507,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="195" spans="1:39" hidden="1">
+    <row r="195" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>982</v>
       </c>
@@ -22605,7 +22602,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="196" spans="1:39" hidden="1">
+    <row r="196" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>985</v>
       </c>
@@ -22700,7 +22697,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="197" spans="1:39" hidden="1">
+    <row r="197" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>990</v>
       </c>
@@ -22795,7 +22792,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="198" spans="1:39" hidden="1">
+    <row r="198" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>995</v>
       </c>
@@ -22893,7 +22890,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="199" spans="1:39" hidden="1">
+    <row r="199" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>378</v>
       </c>
@@ -22991,7 +22988,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="200" spans="1:39" hidden="1">
+    <row r="200" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>1000</v>
       </c>
@@ -23086,7 +23083,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="201" spans="1:39" hidden="1">
+    <row r="201" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>1005</v>
       </c>
@@ -23184,7 +23181,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="202" spans="1:39" hidden="1">
+    <row r="202" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>1011</v>
       </c>
@@ -23279,7 +23276,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="203" spans="1:39" hidden="1">
+    <row r="203" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1015</v>
       </c>
@@ -23374,7 +23371,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="204" spans="1:39" hidden="1">
+    <row r="204" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>384</v>
       </c>
@@ -23472,7 +23469,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="205" spans="1:39" hidden="1">
+    <row r="205" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>1020</v>
       </c>
@@ -23570,7 +23567,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="206" spans="1:39" hidden="1">
+    <row r="206" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>1020</v>
       </c>
@@ -23668,7 +23665,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="207" spans="1:39" hidden="1">
+    <row r="207" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>390</v>
       </c>
@@ -23763,7 +23760,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="208" spans="1:39" hidden="1">
+    <row r="208" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>1025</v>
       </c>
@@ -23858,7 +23855,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="209" spans="1:39" hidden="1">
+    <row r="209" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>395</v>
       </c>
@@ -23956,7 +23953,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="210" spans="1:39" hidden="1">
+    <row r="210" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>400</v>
       </c>
@@ -24054,7 +24051,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="211" spans="1:39" hidden="1">
+    <row r="211" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>1030</v>
       </c>
@@ -24152,7 +24149,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="212" spans="1:39" hidden="1">
+    <row r="212" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>1030</v>
       </c>
@@ -24250,7 +24247,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="213" spans="1:39" hidden="1">
+    <row r="213" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>1037</v>
       </c>
@@ -24345,7 +24342,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="214" spans="1:39" hidden="1">
+    <row r="214" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>1037</v>
       </c>
@@ -24440,7 +24437,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="215" spans="1:39" hidden="1">
+    <row r="215" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>1043</v>
       </c>
@@ -24535,7 +24532,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="216" spans="1:39" hidden="1">
+    <row r="216" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>1047</v>
       </c>
@@ -24630,7 +24627,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="217" spans="1:39" hidden="1">
+    <row r="217" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>1052</v>
       </c>
@@ -24728,7 +24725,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="218" spans="1:39" hidden="1">
+    <row r="218" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>405</v>
       </c>
@@ -24826,7 +24823,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="219" spans="1:39" hidden="1">
+    <row r="219" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>1059</v>
       </c>
@@ -24921,7 +24918,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="220" spans="1:39" hidden="1">
+    <row r="220" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>411</v>
       </c>
@@ -25016,7 +25013,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="221" spans="1:39" hidden="1">
+    <row r="221" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>418</v>
       </c>
@@ -25117,7 +25114,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="222" spans="1:39" hidden="1">
+    <row r="222" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>1066</v>
       </c>
@@ -25215,7 +25212,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="223" spans="1:39" hidden="1">
+    <row r="223" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>1071</v>
       </c>
@@ -25274,22 +25271,25 @@
         <v>430</v>
       </c>
     </row>
-    <row r="251" spans="25:25">
+    <row r="251" spans="25:25" x14ac:dyDescent="0.2">
       <c r="Y251" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM223" xr:uid="{87B7DC3E-A36C-1846-B0DD-7107AEF1D1CD}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="JAMES R DIIORIO WATER RECLAMATION FAC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AM223" xr:uid="{87B7DC3E-A36C-1846-B0DD-7107AEF1D1CD}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="4d95fb05-5706-4269-8c5d-48c42636077e" xsi:nil="true"/>
@@ -25298,15 +25298,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25551,6 +25542,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E5BC3AB-2CCE-499F-B8C2-1C0387FD3409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A35900C-E0AD-40CC-BC89-8EB93FFF6CB2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -25563,14 +25562,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="4d95fb05-5706-4269-8c5d-48c42636077e"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E5BC3AB-2CCE-499F-B8C2-1C0387FD3409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
